--- a/public/StructureDefinition-pghd-alchol-use.xlsx
+++ b/public/StructureDefinition-pghd-alchol-use.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T16:28:41-06:00</t>
+    <t>2026-09-10T16:32:51-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/public/StructureDefinition-pghd-alchol-use.xlsx
+++ b/public/StructureDefinition-pghd-alchol-use.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3488" uniqueCount="605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3488" uniqueCount="606">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-20T16:07:18-05:00</t>
+    <t>2026-10-08T19:53:09-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -984,6 +984,9 @@
   </si>
   <si>
     <t>Observation.code.coding.system</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/uv/phr/CodeSystem/observation-pghd-codes</t>
   </si>
   <si>
     <t>Observation.code.coding:PGHDCode.version</t>
@@ -6370,7 +6373,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>93</v>
@@ -6404,7 +6407,7 @@
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>82</v>
+        <v>313</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -6481,10 +6484,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6601,10 +6604,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6644,7 +6647,7 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>82</v>
@@ -6721,10 +6724,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6841,10 +6844,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6963,13 +6966,13 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>302</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>82</v>
@@ -7087,7 +7090,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>308</v>
@@ -7205,7 +7208,7 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>310</v>
@@ -7325,7 +7328,7 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>312</v>
@@ -7370,7 +7373,7 @@
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>82</v>
@@ -7447,10 +7450,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7567,10 +7570,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7610,7 +7613,7 @@
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>82</v>
@@ -7687,10 +7690,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7807,10 +7810,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7929,10 +7932,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8051,10 +8054,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8077,19 +8080,19 @@
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -8138,7 +8141,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8153,19 +8156,19 @@
         <v>105</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -8173,10 +8176,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8199,16 +8202,16 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8258,7 +8261,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8282,10 +8285,10 @@
         <v>296</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -8293,14 +8296,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8319,19 +8322,19 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8380,7 +8383,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8395,19 +8398,19 @@
         <v>105</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>82</v>
@@ -8415,14 +8418,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8441,19 +8444,19 @@
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8502,7 +8505,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8517,19 +8520,19 @@
         <v>105</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -8537,10 +8540,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8563,16 +8566,16 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8622,7 +8625,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8643,13 +8646,13 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -8657,10 +8660,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8683,17 +8686,17 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8742,7 +8745,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8757,19 +8760,19 @@
         <v>105</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -8777,10 +8780,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8803,19 +8806,19 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8864,7 +8867,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8873,7 +8876,7 @@
         <v>93</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>105</v>
@@ -8882,27 +8885,27 @@
         <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9017,10 +9020,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9137,10 +9140,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9163,19 +9166,19 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9224,7 +9227,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9245,10 +9248,10 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9259,10 +9262,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9288,20 +9291,20 @@
         <v>113</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q59" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="R59" t="s" s="2">
         <v>82</v>
@@ -9325,10 +9328,10 @@
         <v>182</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
@@ -9346,7 +9349,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9367,10 +9370,10 @@
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9381,10 +9384,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9410,14 +9413,14 @@
         <v>206</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9427,7 +9430,7 @@
         <v>82</v>
       </c>
       <c r="S60" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>82</v>
@@ -9466,7 +9469,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9487,10 +9490,10 @@
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9501,10 +9504,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9530,14 +9533,14 @@
         <v>107</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9547,7 +9550,7 @@
         <v>82</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>82</v>
@@ -9586,7 +9589,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9595,7 +9598,7 @@
         <v>93</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>105</v>
@@ -9607,10 +9610,10 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9621,10 +9624,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9650,16 +9653,16 @@
         <v>113</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9708,7 +9711,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9729,10 +9732,10 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9743,10 +9746,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9772,16 +9775,16 @@
         <v>191</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -9806,13 +9809,13 @@
         <v>82</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>82</v>
@@ -9830,7 +9833,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9839,7 +9842,7 @@
         <v>93</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>105</v>
@@ -9854,7 +9857,7 @@
         <v>136</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9865,14 +9868,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9894,16 +9897,16 @@
         <v>191</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>82</v>
@@ -9928,13 +9931,13 @@
         <v>82</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -9952,7 +9955,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9970,27 +9973,27 @@
         <v>82</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10013,19 +10016,19 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
@@ -10074,7 +10077,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10095,10 +10098,10 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10109,10 +10112,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10138,13 +10141,13 @@
         <v>191</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10173,10 +10176,10 @@
         <v>291</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>82</v>
@@ -10194,7 +10197,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10212,27 +10215,27 @@
         <v>82</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10258,16 +10261,16 @@
         <v>191</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10295,10 +10298,10 @@
         <v>291</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
@@ -10316,7 +10319,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10337,10 +10340,10 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10351,10 +10354,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10377,16 +10380,16 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10436,7 +10439,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10454,27 +10457,27 @@
         <v>82</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10497,16 +10500,16 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10556,7 +10559,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10574,27 +10577,27 @@
         <v>82</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10617,19 +10620,19 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -10678,7 +10681,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10690,7 +10693,7 @@
         <v>82</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>82</v>
@@ -10699,10 +10702,10 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10713,10 +10716,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10831,10 +10834,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10951,14 +10954,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10980,10 +10983,10 @@
         <v>139</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>142</v>
@@ -11038,7 +11041,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11073,10 +11076,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11099,13 +11102,13 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11156,7 +11159,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11165,7 +11168,7 @@
         <v>93</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>105</v>
@@ -11177,10 +11180,10 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11191,10 +11194,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11217,13 +11220,13 @@
         <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11274,7 +11277,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11283,7 +11286,7 @@
         <v>93</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>105</v>
@@ -11295,10 +11298,10 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11309,10 +11312,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11338,16 +11341,16 @@
         <v>191</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -11375,10 +11378,10 @@
         <v>117</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>82</v>
@@ -11396,7 +11399,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11414,13 +11417,13 @@
         <v>82</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11431,10 +11434,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11460,16 +11463,16 @@
         <v>191</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>82</v>
@@ -11497,10 +11500,10 @@
         <v>291</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>82</v>
@@ -11518,7 +11521,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11536,13 +11539,13 @@
         <v>82</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11553,10 +11556,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11579,17 +11582,17 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
@@ -11638,7 +11641,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11662,7 +11665,7 @@
         <v>82</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11673,10 +11676,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11702,10 +11705,10 @@
         <v>206</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11756,7 +11759,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11777,10 +11780,10 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -11791,10 +11794,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11817,16 +11820,16 @@
         <v>94</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11876,7 +11879,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11897,10 +11900,10 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -11911,10 +11914,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11937,16 +11940,16 @@
         <v>94</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11996,7 +11999,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12017,10 +12020,10 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
@@ -12031,10 +12034,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12057,19 +12060,19 @@
         <v>94</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
@@ -12118,7 +12121,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12139,10 +12142,10 @@
         <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
@@ -12153,10 +12156,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12271,10 +12274,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12391,14 +12394,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12420,10 +12423,10 @@
         <v>139</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N85" t="s" s="2">
         <v>142</v>
@@ -12478,7 +12481,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12513,10 +12516,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12542,13 +12545,13 @@
         <v>191</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="O86" t="s" s="2">
         <v>290</v>
@@ -12600,7 +12603,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>93</v>
@@ -12618,7 +12621,7 @@
         <v>82</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>296</v>
@@ -12635,10 +12638,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12661,19 +12664,19 @@
         <v>94</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -12722,7 +12725,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12740,27 +12743,27 @@
         <v>82</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12786,16 +12789,16 @@
         <v>191</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -12820,13 +12823,13 @@
         <v>82</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>82</v>
@@ -12844,7 +12847,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12853,7 +12856,7 @@
         <v>93</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>105</v>
@@ -12868,7 +12871,7 @@
         <v>136</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -12879,14 +12882,14 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -12908,16 +12911,16 @@
         <v>191</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
@@ -12942,13 +12945,13 @@
         <v>82</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>82</v>
@@ -12966,7 +12969,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12984,27 +12987,27 @@
         <v>82</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13030,16 +13033,16 @@
         <v>83</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
@@ -13088,7 +13091,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13109,10 +13112,10 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
